--- a/codespace/DetroitRiverCase/results/ch3_fw3_concordant_lda_stratified_confusion_matrix.xlsx
+++ b/codespace/DetroitRiverCase/results/ch3_fw3_concordant_lda_stratified_confusion_matrix.xlsx
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94% (n = 17)</t>
+          <t>100% (n = 17)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
